--- a/docs/templates/人员批量导入模板.xlsx
+++ b/docs/templates/人员批量导入模板.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>1.0（2026-07-25）</t>
+          <t>1.1（2026-07-26，已配套安全批量导入程序）</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>表内不保存初始密码；导入时生成独立强密码，通过受控渠道逐人分发并要求首次使用后重置。</t>
+          <t>表内不保存初始密码；导入时生成独立随机强密码，通过受控渠道逐人分发。当前版本尚未提供药师自助改密。</t>
         </is>
       </c>
     </row>
